--- a/xlsx/v2/org_company_20260413121326.xlsx
+++ b/xlsx/v2/org_company_20260413121326.xlsx
@@ -156,7 +156,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -219,16 +219,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -321,14 +325,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -336,67 +340,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -415,35 +377,11 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -456,222 +394,222 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="0" t="s">
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="0" t="s">
+      <c r="H13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>39</v>
       </c>
     </row>
